--- a/AI工具/Amazon Image Extractor/asin_list.xlsx
+++ b/AI工具/Amazon Image Extractor/asin_list.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="180">
   <si>
     <t>Site</t>
   </si>
@@ -564,6 +564,9 @@
   </si>
   <si>
     <t>B0G5WHNT8K</t>
+  </si>
+  <si>
+    <t>B0D4YSJJMG</t>
   </si>
 </sst>
 </file>
@@ -1177,7 +1180,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment/>
@@ -1188,14 +1191,6 @@
       </extLst>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment/>
-      <extLst>
-        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
-          <etc:displayText val="2"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment/>
       <extLst>
         <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
@@ -1549,8 +1544,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B176"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:B177"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="2" max="2" width="21" customWidth="1"/>
   </cols>
@@ -2583,7 +2578,7 @@
       <c r="A129" t="s">
         <v>125</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="B129" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -2591,7 +2586,7 @@
       <c r="A130" t="s">
         <v>125</v>
       </c>
-      <c r="B130" s="3" t="s">
+      <c r="B130" s="1" t="s">
         <v>132</v>
       </c>
     </row>
@@ -2599,7 +2594,7 @@
       <c r="A131" t="s">
         <v>125</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="B131" s="1" t="s">
         <v>133</v>
       </c>
     </row>
@@ -2607,7 +2602,7 @@
       <c r="A132" t="s">
         <v>125</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="B132" s="1" t="s">
         <v>134</v>
       </c>
     </row>
@@ -2615,7 +2610,7 @@
       <c r="A133" t="s">
         <v>125</v>
       </c>
-      <c r="B133" s="3" t="s">
+      <c r="B133" s="1" t="s">
         <v>135</v>
       </c>
     </row>
@@ -2623,7 +2618,7 @@
       <c r="A134" t="s">
         <v>125</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="B134" s="1" t="s">
         <v>136</v>
       </c>
     </row>
@@ -2631,7 +2626,7 @@
       <c r="A135" t="s">
         <v>125</v>
       </c>
-      <c r="B135" s="3" t="s">
+      <c r="B135" s="1" t="s">
         <v>137</v>
       </c>
     </row>
@@ -2639,7 +2634,7 @@
       <c r="A136" t="s">
         <v>125</v>
       </c>
-      <c r="B136" s="3" t="s">
+      <c r="B136" s="1" t="s">
         <v>138</v>
       </c>
     </row>
@@ -2647,7 +2642,7 @@
       <c r="A137" t="s">
         <v>125</v>
       </c>
-      <c r="B137" s="3" t="s">
+      <c r="B137" s="1" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2655,7 +2650,7 @@
       <c r="A138" t="s">
         <v>125</v>
       </c>
-      <c r="B138" s="3" t="s">
+      <c r="B138" s="1" t="s">
         <v>140</v>
       </c>
     </row>
@@ -2663,7 +2658,7 @@
       <c r="A139" t="s">
         <v>125</v>
       </c>
-      <c r="B139" s="3" t="s">
+      <c r="B139" s="1" t="s">
         <v>141</v>
       </c>
     </row>
@@ -2671,7 +2666,7 @@
       <c r="A140" t="s">
         <v>125</v>
       </c>
-      <c r="B140" s="3" t="s">
+      <c r="B140" s="1" t="s">
         <v>142</v>
       </c>
     </row>
@@ -2679,7 +2674,7 @@
       <c r="A141" t="s">
         <v>125</v>
       </c>
-      <c r="B141" s="3" t="s">
+      <c r="B141" s="1" t="s">
         <v>143</v>
       </c>
     </row>
@@ -2687,7 +2682,7 @@
       <c r="A142" t="s">
         <v>125</v>
       </c>
-      <c r="B142" s="3" t="s">
+      <c r="B142" s="1" t="s">
         <v>144</v>
       </c>
     </row>
@@ -2695,7 +2690,7 @@
       <c r="A143" t="s">
         <v>125</v>
       </c>
-      <c r="B143" s="3" t="s">
+      <c r="B143" s="1" t="s">
         <v>145</v>
       </c>
     </row>
@@ -2703,7 +2698,7 @@
       <c r="A144" t="s">
         <v>125</v>
       </c>
-      <c r="B144" s="3" t="s">
+      <c r="B144" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2711,7 +2706,7 @@
       <c r="A145" t="s">
         <v>125</v>
       </c>
-      <c r="B145" s="3" t="s">
+      <c r="B145" s="1" t="s">
         <v>147</v>
       </c>
     </row>
@@ -2719,7 +2714,7 @@
       <c r="A146" t="s">
         <v>125</v>
       </c>
-      <c r="B146" s="3" t="s">
+      <c r="B146" s="1" t="s">
         <v>148</v>
       </c>
     </row>
@@ -2727,7 +2722,7 @@
       <c r="A147" t="s">
         <v>125</v>
       </c>
-      <c r="B147" s="3" t="s">
+      <c r="B147" s="1" t="s">
         <v>149</v>
       </c>
     </row>
@@ -2735,7 +2730,7 @@
       <c r="A148" t="s">
         <v>125</v>
       </c>
-      <c r="B148" s="3" t="s">
+      <c r="B148" s="1" t="s">
         <v>150</v>
       </c>
     </row>
@@ -2743,7 +2738,7 @@
       <c r="A149" t="s">
         <v>125</v>
       </c>
-      <c r="B149" s="3" t="s">
+      <c r="B149" s="1" t="s">
         <v>151</v>
       </c>
     </row>
@@ -2751,7 +2746,7 @@
       <c r="A150" t="s">
         <v>125</v>
       </c>
-      <c r="B150" s="3" t="s">
+      <c r="B150" s="1" t="s">
         <v>152</v>
       </c>
     </row>
@@ -2759,7 +2754,7 @@
       <c r="A151" t="s">
         <v>125</v>
       </c>
-      <c r="B151" s="3" t="s">
+      <c r="B151" s="1" t="s">
         <v>153</v>
       </c>
     </row>
@@ -2767,7 +2762,7 @@
       <c r="A152" t="s">
         <v>125</v>
       </c>
-      <c r="B152" s="3" t="s">
+      <c r="B152" s="1" t="s">
         <v>154</v>
       </c>
     </row>
@@ -2775,7 +2770,7 @@
       <c r="A153" t="s">
         <v>125</v>
       </c>
-      <c r="B153" s="3" t="s">
+      <c r="B153" s="1" t="s">
         <v>155</v>
       </c>
     </row>
@@ -2783,7 +2778,7 @@
       <c r="A154" t="s">
         <v>125</v>
       </c>
-      <c r="B154" s="3" t="s">
+      <c r="B154" s="1" t="s">
         <v>156</v>
       </c>
     </row>
@@ -2791,7 +2786,7 @@
       <c r="A155" t="s">
         <v>125</v>
       </c>
-      <c r="B155" s="3" t="s">
+      <c r="B155" s="1" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2799,7 +2794,7 @@
       <c r="A156" t="s">
         <v>125</v>
       </c>
-      <c r="B156" s="3" t="s">
+      <c r="B156" s="1" t="s">
         <v>158</v>
       </c>
     </row>
@@ -2807,7 +2802,7 @@
       <c r="A157" t="s">
         <v>125</v>
       </c>
-      <c r="B157" s="3" t="s">
+      <c r="B157" s="1" t="s">
         <v>159</v>
       </c>
     </row>
@@ -2815,7 +2810,7 @@
       <c r="A158" t="s">
         <v>125</v>
       </c>
-      <c r="B158" s="3" t="s">
+      <c r="B158" s="1" t="s">
         <v>160</v>
       </c>
     </row>
@@ -2823,7 +2818,7 @@
       <c r="A159" t="s">
         <v>125</v>
       </c>
-      <c r="B159" s="3" t="s">
+      <c r="B159" s="1" t="s">
         <v>161</v>
       </c>
     </row>
@@ -2831,7 +2826,7 @@
       <c r="A160" t="s">
         <v>125</v>
       </c>
-      <c r="B160" s="3" t="s">
+      <c r="B160" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2839,7 +2834,7 @@
       <c r="A161" t="s">
         <v>125</v>
       </c>
-      <c r="B161" s="3" t="s">
+      <c r="B161" s="1" t="s">
         <v>163</v>
       </c>
     </row>
@@ -2847,7 +2842,7 @@
       <c r="A162" t="s">
         <v>125</v>
       </c>
-      <c r="B162" s="3" t="s">
+      <c r="B162" s="1" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2855,7 +2850,7 @@
       <c r="A163" t="s">
         <v>125</v>
       </c>
-      <c r="B163" s="3" t="s">
+      <c r="B163" s="1" t="s">
         <v>165</v>
       </c>
     </row>
@@ -2863,7 +2858,7 @@
       <c r="A164" t="s">
         <v>125</v>
       </c>
-      <c r="B164" s="3" t="s">
+      <c r="B164" s="1" t="s">
         <v>166</v>
       </c>
     </row>
@@ -2871,7 +2866,7 @@
       <c r="A165" t="s">
         <v>125</v>
       </c>
-      <c r="B165" s="3" t="s">
+      <c r="B165" s="1" t="s">
         <v>167</v>
       </c>
     </row>
@@ -2879,7 +2874,7 @@
       <c r="A166" t="s">
         <v>125</v>
       </c>
-      <c r="B166" s="3" t="s">
+      <c r="B166" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -2887,7 +2882,7 @@
       <c r="A167" t="s">
         <v>125</v>
       </c>
-      <c r="B167" s="3" t="s">
+      <c r="B167" s="1" t="s">
         <v>169</v>
       </c>
     </row>
@@ -2895,7 +2890,7 @@
       <c r="A168" t="s">
         <v>125</v>
       </c>
-      <c r="B168" s="3" t="s">
+      <c r="B168" s="1" t="s">
         <v>170</v>
       </c>
     </row>
@@ -2903,7 +2898,7 @@
       <c r="A169" t="s">
         <v>125</v>
       </c>
-      <c r="B169" s="3" t="s">
+      <c r="B169" s="1" t="s">
         <v>171</v>
       </c>
     </row>
@@ -2911,7 +2906,7 @@
       <c r="A170" t="s">
         <v>125</v>
       </c>
-      <c r="B170" s="3" t="s">
+      <c r="B170" s="1" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2919,7 +2914,7 @@
       <c r="A171" t="s">
         <v>125</v>
       </c>
-      <c r="B171" s="3" t="s">
+      <c r="B171" s="1" t="s">
         <v>173</v>
       </c>
     </row>
@@ -2927,7 +2922,7 @@
       <c r="A172" t="s">
         <v>125</v>
       </c>
-      <c r="B172" s="3" t="s">
+      <c r="B172" s="1" t="s">
         <v>174</v>
       </c>
     </row>
@@ -2935,7 +2930,7 @@
       <c r="A173" t="s">
         <v>125</v>
       </c>
-      <c r="B173" s="3" t="s">
+      <c r="B173" s="1" t="s">
         <v>175</v>
       </c>
     </row>
@@ -2943,7 +2938,7 @@
       <c r="A174" t="s">
         <v>125</v>
       </c>
-      <c r="B174" s="3" t="s">
+      <c r="B174" s="1" t="s">
         <v>176</v>
       </c>
     </row>
@@ -2951,7 +2946,7 @@
       <c r="A175" t="s">
         <v>125</v>
       </c>
-      <c r="B175" s="3" t="s">
+      <c r="B175" s="1" t="s">
         <v>177</v>
       </c>
     </row>
@@ -2959,8 +2954,16 @@
       <c r="A176" t="s">
         <v>125</v>
       </c>
-      <c r="B176" s="3" t="s">
+      <c r="B176" s="1" t="s">
         <v>178</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" t="s">
+        <v>2</v>
+      </c>
+      <c r="B177" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
